--- a/Trade.xlsx
+++ b/Trade.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\b121803\Desktop\Note\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SaveCode\Phaser\idle-game\idle\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="56">
   <si>
     <t>Giá mua</t>
   </si>
@@ -118,24 +118,6 @@
   </si>
   <si>
     <t>% Lợi nhuận</t>
-  </si>
-  <si>
-    <t>Expert's Light Crossbow</t>
-  </si>
-  <si>
-    <t>Expert's Dagger [5.0]</t>
-  </si>
-  <si>
-    <t>Expert's Dagger Pair [5.0]</t>
-  </si>
-  <si>
-    <t>Expert's Claws [5.0]</t>
-  </si>
-  <si>
-    <t>Expert's Great Hammer [5.0]</t>
-  </si>
-  <si>
-    <t>Expert's Iron-clad Staff [5.0]</t>
   </si>
   <si>
     <r>
@@ -250,12 +232,6 @@
     </r>
   </si>
   <si>
-    <t>Expert's Spear [5.0]</t>
-  </si>
-  <si>
-    <t>Expert's Glaive [5.0]</t>
-  </si>
-  <si>
     <t>Price</t>
   </si>
   <si>
@@ -280,28 +256,37 @@
     <t>Check</t>
   </si>
   <si>
-    <t>✅</t>
-  </si>
-  <si>
-    <t>Expert's Battle Bracers [5.0]</t>
-  </si>
-  <si>
     <t>Total</t>
   </si>
   <si>
     <t>30C</t>
   </si>
   <si>
-    <t>120K-30C</t>
-  </si>
-  <si>
     <t>City</t>
   </si>
   <si>
     <t>FS</t>
   </si>
   <si>
-    <t>LYM</t>
+    <t>Expert's Heavy Crossbow [5.1]</t>
+  </si>
+  <si>
+    <t>Expert's Spear [5.1]</t>
+  </si>
+  <si>
+    <t>Expert's Infernal Staff [5.1]</t>
+  </si>
+  <si>
+    <t>TF</t>
+  </si>
+  <si>
+    <t>Expert's Great Fire Staff [5.1]</t>
+  </si>
+  <si>
+    <t>40P</t>
+  </si>
+  <si>
+    <t>40K-30C-80P</t>
   </si>
 </sst>
 </file>
@@ -314,7 +299,7 @@
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -427,6 +412,13 @@
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF081B3A"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="163"/>
     </font>
   </fonts>
   <fills count="4">
@@ -691,7 +683,7 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -811,6 +803,9 @@
     <xf numFmtId="10" fontId="13" fillId="2" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Accent6" xfId="4" builtinId="49"/>
@@ -986,6 +981,25 @@
         </bottom>
         <vertical/>
         <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF7F7F7F"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FF7F7F7F"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF7F7F7F"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -1059,28 +1073,39 @@
       </border>
     </dxf>
     <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FF7F7F7F"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF7F7F7F"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF7F7F7F"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF7F7F7F"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF7F7F7F"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
       </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF7F7F7F"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FF7F7F7F"/>
-        </top>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <bottom style="thin">
           <color rgb="FF7F7F7F"/>
         </bottom>
       </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -1093,36 +1118,6 @@
         </right>
         <top/>
         <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color rgb="FF7F7F7F"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF7F7F7F"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FF7F7F7F"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF7F7F7F"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF7F7F7F"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF7F7F7F"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -1494,22 +1489,22 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:K11" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11" headerRowBorderDxfId="14" tableBorderDxfId="15" totalsRowBorderDxfId="13" headerRowCellStyle="Accent6" dataCellStyle="Good">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:K11" totalsRowShown="0" headerRowDxfId="15" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12" totalsRowBorderDxfId="11" headerRowCellStyle="Accent6" dataCellStyle="Good">
   <autoFilter ref="A1:K11"/>
   <sortState ref="A2:D10">
     <sortCondition descending="1" ref="C1:C10"/>
   </sortState>
   <tableColumns count="11">
-    <tableColumn id="1" name="Item" dataDxfId="9" dataCellStyle="Good"/>
-    <tableColumn id="4" name="Price" dataDxfId="8" dataCellStyle="Good"/>
-    <tableColumn id="2" name="Lợi nhuận" dataDxfId="1" dataCellStyle="Good"/>
-    <tableColumn id="3" name="% Lợi nhuận" dataDxfId="10" dataCellStyle="Good"/>
-    <tableColumn id="5" name="Gỗ" dataDxfId="7" dataCellStyle="Good"/>
-    <tableColumn id="6" name="Quặng" dataDxfId="6" dataCellStyle="Good"/>
-    <tableColumn id="7" name="Bông" dataDxfId="5" dataCellStyle="Good"/>
-    <tableColumn id="8" name="Da" dataDxfId="4" dataCellStyle="Good"/>
-    <tableColumn id="9" name="Sách" dataDxfId="3" dataCellStyle="Good"/>
-    <tableColumn id="10" name="Check" dataDxfId="2" dataCellStyle="Good"/>
+    <tableColumn id="1" name="Item" dataDxfId="10" dataCellStyle="Good"/>
+    <tableColumn id="4" name="Price" dataDxfId="9" dataCellStyle="Good"/>
+    <tableColumn id="2" name="Lợi nhuận" dataDxfId="8" dataCellStyle="Good"/>
+    <tableColumn id="3" name="% Lợi nhuận" dataDxfId="7" dataCellStyle="Good"/>
+    <tableColumn id="5" name="Gỗ" dataDxfId="6" dataCellStyle="Good"/>
+    <tableColumn id="6" name="Quặng" dataDxfId="5" dataCellStyle="Good"/>
+    <tableColumn id="7" name="Bông" dataDxfId="4" dataCellStyle="Good"/>
+    <tableColumn id="8" name="Da" dataDxfId="3" dataCellStyle="Good"/>
+    <tableColumn id="9" name="Sách" dataDxfId="2" dataCellStyle="Good"/>
+    <tableColumn id="10" name="Check" dataDxfId="1" dataCellStyle="Good"/>
     <tableColumn id="11" name="City" dataDxfId="0" dataCellStyle="Good"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2632,7 +2627,7 @@
         <v>9</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C1" s="29" t="s">
         <v>7</v>
@@ -2641,60 +2636,58 @@
         <v>29</v>
       </c>
       <c r="E1" s="37" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F1" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="I1" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="J1" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="K1" s="29" t="s">
         <v>47</v>
-      </c>
-      <c r="G1" s="37" t="s">
-        <v>48</v>
-      </c>
-      <c r="H1" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="I1" s="37" t="s">
-        <v>50</v>
-      </c>
-      <c r="J1" s="37" t="s">
-        <v>52</v>
-      </c>
-      <c r="K1" s="29" t="s">
-        <v>58</v>
       </c>
       <c r="M1" s="4"/>
       <c r="N1" s="4"/>
       <c r="O1" s="4"/>
       <c r="P1" s="4"/>
     </row>
-    <row r="2" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="35" t="s">
-        <v>31</v>
+    <row r="2" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="43" t="s">
+        <v>49</v>
       </c>
       <c r="B2" s="33">
-        <v>39600</v>
-      </c>
-      <c r="C2" s="31">
-        <v>1109434</v>
-      </c>
-      <c r="D2" s="32">
-        <v>0.35049999999999998</v>
-      </c>
-      <c r="E2" s="31"/>
+        <v>88237</v>
+      </c>
+      <c r="C2" s="44">
+        <v>2692231</v>
+      </c>
+      <c r="D2" s="45">
+        <v>1.5584</v>
+      </c>
+      <c r="E2" s="31">
+        <v>757</v>
+      </c>
       <c r="F2" s="31">
-        <v>906</v>
+        <v>455</v>
       </c>
       <c r="G2" s="31"/>
-      <c r="H2" s="31">
-        <v>906</v>
-      </c>
+      <c r="H2" s="31"/>
       <c r="I2" s="31" t="s">
-        <v>56</v>
-      </c>
-      <c r="J2" s="39" t="s">
-        <v>53</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="J2" s="39"/>
       <c r="K2" s="39" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
@@ -2703,112 +2696,98 @@
     </row>
     <row r="3" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="35" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B3" s="33">
-        <v>58300</v>
-      </c>
-      <c r="C3" s="31">
-        <v>1497909</v>
-      </c>
-      <c r="D3" s="32">
-        <v>0.3448</v>
-      </c>
-      <c r="E3" s="31"/>
+        <v>56217</v>
+      </c>
+      <c r="C3" s="44">
+        <v>944989</v>
+      </c>
+      <c r="D3" s="45">
+        <v>0.50349999999999995</v>
+      </c>
+      <c r="E3" s="31">
+        <v>606</v>
+      </c>
       <c r="F3" s="31">
-        <v>906</v>
+        <v>303</v>
       </c>
       <c r="G3" s="31"/>
-      <c r="H3" s="31">
-        <v>1509</v>
-      </c>
+      <c r="H3" s="31"/>
       <c r="I3" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="J3" s="39" t="s">
-        <v>53</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="J3" s="39"/>
       <c r="K3" s="38" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="B4" s="33">
-        <v>50500</v>
-      </c>
-      <c r="C4" s="31">
-        <v>1264197</v>
-      </c>
-      <c r="D4" s="32">
-        <v>0.30059999999999998</v>
-      </c>
-      <c r="E4" s="31"/>
+        <v>65337</v>
+      </c>
+      <c r="C4" s="44">
+        <v>936227</v>
+      </c>
+      <c r="D4" s="45">
+        <v>0.34350000000000003</v>
+      </c>
+      <c r="E4" s="31">
+        <v>757</v>
+      </c>
       <c r="F4" s="31">
-        <v>1208</v>
+        <v>455</v>
       </c>
       <c r="G4" s="31"/>
-      <c r="H4" s="31">
-        <v>1208</v>
-      </c>
+      <c r="H4" s="31"/>
       <c r="I4" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="J4" s="39" t="s">
-        <v>53</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="J4" s="39"/>
       <c r="K4" s="39" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="L4" s="22"/>
     </row>
     <row r="5" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="B5" s="33">
-        <v>46716</v>
-      </c>
-      <c r="C5" s="31">
-        <v>1330938</v>
-      </c>
-      <c r="D5" s="32">
-        <v>0.3972</v>
-      </c>
-      <c r="E5" s="31"/>
+        <v>60696</v>
+      </c>
+      <c r="C5" s="44">
+        <v>719261</v>
+      </c>
+      <c r="D5" s="45">
+        <v>0.26540000000000002</v>
+      </c>
+      <c r="E5" s="31">
+        <v>757</v>
+      </c>
       <c r="F5" s="31">
-        <v>1509</v>
-      </c>
-      <c r="G5" s="31">
-        <v>906</v>
-      </c>
+        <v>455</v>
+      </c>
+      <c r="G5" s="31"/>
       <c r="H5" s="31"/>
       <c r="I5" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="J5" s="39" t="s">
-        <v>53</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="J5" s="39"/>
       <c r="K5" s="38" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="L5" s="27"/>
     </row>
     <row r="6" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="B6" s="33">
-        <v>43490</v>
-      </c>
-      <c r="C6" s="31">
-        <v>1216550</v>
-      </c>
-      <c r="D6" s="32">
-        <v>0.33979999999999999</v>
-      </c>
+      <c r="A6" s="35"/>
+      <c r="B6" s="33"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="32"/>
       <c r="E6" s="31"/>
       <c r="F6" s="31"/>
       <c r="G6" s="31"/>
@@ -2819,18 +2798,10 @@
       <c r="L6" s="27"/>
     </row>
     <row r="7" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="33">
-        <v>50763</v>
-      </c>
-      <c r="C7" s="31">
-        <v>1155937</v>
-      </c>
-      <c r="D7" s="32">
-        <v>0.26629999999999998</v>
-      </c>
+      <c r="A7" s="35"/>
+      <c r="B7" s="33"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="32"/>
       <c r="E7" s="31"/>
       <c r="F7" s="31"/>
       <c r="G7" s="31"/>
@@ -2841,18 +2812,10 @@
       <c r="L7" s="27"/>
     </row>
     <row r="8" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="35" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="33">
-        <v>33289</v>
-      </c>
-      <c r="C8" s="31">
-        <v>944823</v>
-      </c>
-      <c r="D8" s="32">
-        <v>0.39510000000000001</v>
-      </c>
+      <c r="A8" s="35"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="32"/>
       <c r="E8" s="31"/>
       <c r="F8" s="31"/>
       <c r="G8" s="31"/>
@@ -2863,18 +2826,10 @@
       <c r="L8" s="27"/>
     </row>
     <row r="9" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="35" t="s">
-        <v>43</v>
-      </c>
-      <c r="B9" s="33">
-        <v>31043</v>
-      </c>
-      <c r="C9" s="31">
-        <v>837996</v>
-      </c>
-      <c r="D9" s="32">
-        <v>0.3221</v>
-      </c>
+      <c r="A9" s="35"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="32"/>
       <c r="E9" s="31"/>
       <c r="F9" s="31"/>
       <c r="G9" s="31"/>
@@ -2885,18 +2840,10 @@
       <c r="L9" s="27"/>
     </row>
     <row r="10" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" s="34">
-        <v>51855</v>
-      </c>
-      <c r="C10" s="31">
-        <v>806349</v>
-      </c>
-      <c r="D10" s="32">
-        <v>0.18360000000000001</v>
-      </c>
+      <c r="A10" s="36"/>
+      <c r="B10" s="34"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="32"/>
       <c r="E10" s="31"/>
       <c r="F10" s="31"/>
       <c r="G10" s="31"/>
@@ -2908,29 +2855,29 @@
     </row>
     <row r="11" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="41" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B11" s="34"/>
       <c r="C11" s="40"/>
       <c r="D11" s="42"/>
       <c r="E11" s="40">
         <f>SUM(E2:E10)</f>
-        <v>0</v>
+        <v>2877</v>
       </c>
       <c r="F11" s="40">
-        <f t="shared" ref="F11:I11" si="0">SUM(F2:F10)</f>
-        <v>4529</v>
+        <f t="shared" ref="F11:H11" si="0">SUM(F2:F10)</f>
+        <v>1668</v>
       </c>
       <c r="G11" s="40">
         <f t="shared" si="0"/>
-        <v>906</v>
+        <v>0</v>
       </c>
       <c r="H11" s="40">
         <f t="shared" si="0"/>
-        <v>3623</v>
+        <v>0</v>
       </c>
       <c r="I11" s="40" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J11" s="40"/>
       <c r="K11" s="40"/>
@@ -3046,37 +2993,37 @@
     <row r="2" spans="17:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="17:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="Q3" s="25" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="17:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="Q4" s="25" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="17:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="Q5" s="24" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="17:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="Q6" s="24" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="17:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="Q7" s="25" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="17:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="Q8" s="25" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="17:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="Q9" s="25" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/Trade.xlsx
+++ b/Trade.xlsx
@@ -1949,7 +1949,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="42">
-        <v>2118</v>
+        <v>2000</v>
       </c>
       <c r="C3" s="34">
         <v>2000</v>
@@ -1958,7 +1958,7 @@
         <v>39</v>
       </c>
       <c r="E3" s="34">
-        <v>385</v>
+        <v>400</v>
       </c>
       <c r="F3" s="35">
         <v>1267</v>
@@ -1967,30 +1967,30 @@
         <v>34</v>
       </c>
       <c r="H3" s="34">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="I3" s="35">
         <v>3799</v>
       </c>
       <c r="J3" s="34">
         <f>E3*F3+H3*I3</f>
-        <v>3230673</v>
+        <v>3280070</v>
       </c>
       <c r="K3" s="36">
         <f>C3*B3</f>
-        <v>4236000</v>
+        <v>4000000</v>
       </c>
       <c r="L3" s="36">
         <f>K3-J3</f>
-        <v>1005327</v>
+        <v>719930</v>
       </c>
       <c r="M3" s="43">
         <f>J3/C3</f>
-        <v>1615.3364999999999</v>
+        <v>1640.0350000000001</v>
       </c>
       <c r="N3" s="40">
         <f>(B3-M3)</f>
-        <v>502.66350000000011</v>
+        <v>359.96499999999992</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -1998,7 +1998,7 @@
         <v>43</v>
       </c>
       <c r="B4" s="42">
-        <v>2505</v>
+        <v>2400</v>
       </c>
       <c r="C4" s="34">
         <v>2000</v>
@@ -2007,7 +2007,7 @@
         <v>44</v>
       </c>
       <c r="E4" s="34">
-        <v>485</v>
+        <v>290</v>
       </c>
       <c r="F4" s="35">
         <v>1267</v>
@@ -2016,73 +2016,79 @@
         <v>45</v>
       </c>
       <c r="H4" s="34">
-        <v>900</v>
+        <v>910</v>
       </c>
       <c r="I4" s="35">
         <v>3799</v>
       </c>
       <c r="J4" s="34">
         <f t="shared" ref="J4:J6" si="0">E4*F4+H4*I4</f>
-        <v>4033595</v>
+        <v>3824520</v>
       </c>
       <c r="K4" s="36">
         <f t="shared" ref="K4:K6" si="1">C4*B4</f>
-        <v>5010000</v>
+        <v>4800000</v>
       </c>
       <c r="L4" s="36">
         <f t="shared" ref="L4:L6" si="2">K4-J4</f>
-        <v>976405</v>
+        <v>975480</v>
       </c>
       <c r="M4" s="43">
         <f t="shared" ref="M4:M6" si="3">J4/C4</f>
-        <v>2016.7974999999999</v>
+        <v>1912.26</v>
       </c>
       <c r="N4" s="40">
         <f t="shared" ref="N4:N6" si="4">(B4-M4)</f>
-        <v>488.2025000000001</v>
+        <v>487.74</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="42"/>
+      <c r="B5" s="42">
+        <v>2200</v>
+      </c>
       <c r="C5" s="34">
         <v>2000</v>
       </c>
       <c r="D5" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="E5" s="34"/>
+      <c r="E5" s="34">
+        <v>650</v>
+      </c>
       <c r="F5" s="35">
         <v>1267</v>
       </c>
       <c r="G5" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="H5" s="34"/>
+      <c r="H5" s="34">
+        <v>730</v>
+      </c>
       <c r="I5" s="35">
         <v>3799</v>
       </c>
       <c r="J5" s="34">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3596820</v>
       </c>
       <c r="K5" s="36">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4400000</v>
       </c>
       <c r="L5" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>803180</v>
       </c>
       <c r="M5" s="43">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1798.41</v>
       </c>
       <c r="N5" s="40">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>401.58999999999992</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
